--- a/src/timetables/TTFINAL.xlsx
+++ b/src/timetables/TTFINAL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mr_man\Desktop\invigilation-auto\src\timetables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{869C0023-BC4F-46DC-9C1E-D00FF01BAA0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C80D197A-B538-4F26-B461-8DC4D9C9D1F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{56AEB27E-0B57-46B5-9DB8-F1AD67B47E0F}"/>
   </bookViews>
@@ -161,7 +161,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5660" uniqueCount="1458">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5695" uniqueCount="1458">
   <si>
     <t>Monday, 17 August 2026</t>
   </si>
@@ -42296,6 +42296,9 @@
       <c r="E16">
         <v>75</v>
       </c>
+      <c r="F16" t="s">
+        <v>39</v>
+      </c>
       <c r="G16">
         <v>82.5</v>
       </c>
@@ -42316,6 +42319,9 @@
       <c r="E17">
         <v>80</v>
       </c>
+      <c r="F17" t="s">
+        <v>39</v>
+      </c>
       <c r="G17">
         <v>88</v>
       </c>
@@ -42336,6 +42342,9 @@
       <c r="E18">
         <v>82</v>
       </c>
+      <c r="F18" t="s">
+        <v>39</v>
+      </c>
       <c r="G18">
         <v>90.2</v>
       </c>
@@ -42356,6 +42365,9 @@
       <c r="E19">
         <v>37</v>
       </c>
+      <c r="F19" t="s">
+        <v>39</v>
+      </c>
       <c r="G19">
         <v>40.700000000000003</v>
       </c>
@@ -42920,6 +42932,9 @@
       <c r="E48">
         <v>56</v>
       </c>
+      <c r="F48" t="s">
+        <v>39</v>
+      </c>
       <c r="G48">
         <v>61.600000000000009</v>
       </c>
@@ -42940,6 +42955,9 @@
       <c r="E49">
         <v>130</v>
       </c>
+      <c r="F49" t="s">
+        <v>39</v>
+      </c>
       <c r="G49">
         <v>143</v>
       </c>
@@ -44893,6 +44911,9 @@
       <c r="E140">
         <v>32</v>
       </c>
+      <c r="F140" t="s">
+        <v>39</v>
+      </c>
       <c r="G140">
         <v>35.200000000000003</v>
       </c>
@@ -48724,6 +48745,9 @@
       <c r="E317">
         <v>82</v>
       </c>
+      <c r="F317" t="s">
+        <v>39</v>
+      </c>
       <c r="G317">
         <v>90.2</v>
       </c>
@@ -48744,6 +48768,9 @@
       <c r="E318">
         <v>250</v>
       </c>
+      <c r="F318" t="s">
+        <v>39</v>
+      </c>
       <c r="G318">
         <v>275</v>
       </c>
@@ -48764,6 +48791,9 @@
       <c r="E319">
         <v>65</v>
       </c>
+      <c r="F319" t="s">
+        <v>39</v>
+      </c>
       <c r="G319">
         <v>71.5</v>
       </c>
@@ -48784,6 +48814,9 @@
       <c r="E320">
         <v>95</v>
       </c>
+      <c r="F320" t="s">
+        <v>39</v>
+      </c>
       <c r="G320">
         <v>104.50000000000001</v>
       </c>
@@ -48804,6 +48837,9 @@
       <c r="E321">
         <v>132</v>
       </c>
+      <c r="F321" t="s">
+        <v>39</v>
+      </c>
       <c r="G321">
         <v>145.20000000000002</v>
       </c>
@@ -48824,6 +48860,9 @@
       <c r="E322">
         <v>83</v>
       </c>
+      <c r="F322" t="s">
+        <v>39</v>
+      </c>
       <c r="G322">
         <v>91.300000000000011</v>
       </c>
@@ -48844,6 +48883,9 @@
       <c r="E323">
         <v>57</v>
       </c>
+      <c r="F323" t="s">
+        <v>39</v>
+      </c>
       <c r="G323">
         <v>62.7</v>
       </c>
@@ -48864,6 +48906,9 @@
       <c r="E324">
         <v>255</v>
       </c>
+      <c r="F324" t="s">
+        <v>39</v>
+      </c>
       <c r="G324">
         <v>280.5</v>
       </c>
@@ -48884,6 +48929,9 @@
       <c r="E325">
         <v>150</v>
       </c>
+      <c r="F325" t="s">
+        <v>39</v>
+      </c>
       <c r="G325">
         <v>165</v>
       </c>
@@ -48904,6 +48952,9 @@
       <c r="E326">
         <v>175</v>
       </c>
+      <c r="F326" t="s">
+        <v>39</v>
+      </c>
       <c r="G326">
         <v>192.50000000000003</v>
       </c>
@@ -48924,6 +48975,9 @@
       <c r="E327">
         <v>155</v>
       </c>
+      <c r="F327" t="s">
+        <v>39</v>
+      </c>
       <c r="G327">
         <v>170.5</v>
       </c>
@@ -48944,6 +48998,9 @@
       <c r="E328">
         <v>75</v>
       </c>
+      <c r="F328" t="s">
+        <v>39</v>
+      </c>
       <c r="G328">
         <v>82.5</v>
       </c>
@@ -48964,6 +49021,9 @@
       <c r="E329">
         <v>80</v>
       </c>
+      <c r="F329" t="s">
+        <v>39</v>
+      </c>
       <c r="G329">
         <v>88</v>
       </c>
@@ -50735,6 +50795,9 @@
       <c r="E414">
         <v>128</v>
       </c>
+      <c r="F414" t="s">
+        <v>39</v>
+      </c>
       <c r="G414">
         <v>140.80000000000001</v>
       </c>
@@ -50755,6 +50818,9 @@
       <c r="E415">
         <v>136</v>
       </c>
+      <c r="F415" t="s">
+        <v>39</v>
+      </c>
       <c r="G415">
         <v>149.60000000000002</v>
       </c>
@@ -50775,6 +50841,9 @@
       <c r="E416">
         <v>245</v>
       </c>
+      <c r="F416" t="s">
+        <v>39</v>
+      </c>
       <c r="G416">
         <v>269.5</v>
       </c>
@@ -50795,6 +50864,9 @@
       <c r="E417">
         <v>120</v>
       </c>
+      <c r="F417" t="s">
+        <v>39</v>
+      </c>
       <c r="G417">
         <v>132</v>
       </c>
@@ -50815,6 +50887,9 @@
       <c r="E418">
         <v>262</v>
       </c>
+      <c r="F418" t="s">
+        <v>39</v>
+      </c>
       <c r="G418">
         <v>288.20000000000005</v>
       </c>
@@ -51081,6 +51156,9 @@
       <c r="E431">
         <v>85</v>
       </c>
+      <c r="F431" t="s">
+        <v>663</v>
+      </c>
       <c r="G431">
         <v>93.500000000000014</v>
       </c>
@@ -51101,6 +51179,9 @@
       <c r="E432">
         <v>295</v>
       </c>
+      <c r="F432" t="s">
+        <v>663</v>
+      </c>
       <c r="G432">
         <v>324.5</v>
       </c>
@@ -51121,6 +51202,9 @@
       <c r="E433">
         <v>83</v>
       </c>
+      <c r="F433" t="s">
+        <v>663</v>
+      </c>
       <c r="G433">
         <v>91.300000000000011</v>
       </c>
@@ -51141,6 +51225,9 @@
       <c r="E434">
         <v>125</v>
       </c>
+      <c r="F434" t="s">
+        <v>663</v>
+      </c>
       <c r="G434">
         <v>137.5</v>
       </c>
@@ -51161,6 +51248,9 @@
       <c r="E435">
         <v>100</v>
       </c>
+      <c r="F435" t="s">
+        <v>663</v>
+      </c>
       <c r="G435">
         <v>110.00000000000001</v>
       </c>
@@ -51181,6 +51271,9 @@
       <c r="E436">
         <v>103</v>
       </c>
+      <c r="F436" t="s">
+        <v>663</v>
+      </c>
       <c r="G436">
         <v>113.30000000000001</v>
       </c>
@@ -51551,6 +51644,9 @@
       <c r="E455">
         <v>225</v>
       </c>
+      <c r="F455" t="s">
+        <v>39</v>
+      </c>
       <c r="G455">
         <v>247.50000000000003</v>
       </c>
@@ -51571,6 +51667,9 @@
       <c r="E456">
         <v>130</v>
       </c>
+      <c r="F456" t="s">
+        <v>39</v>
+      </c>
       <c r="G456">
         <v>143</v>
       </c>
@@ -51591,6 +51690,9 @@
       <c r="E457">
         <v>130</v>
       </c>
+      <c r="F457" t="s">
+        <v>39</v>
+      </c>
       <c r="G457">
         <v>143</v>
       </c>
@@ -51610,6 +51712,9 @@
       </c>
       <c r="E458">
         <v>75</v>
+      </c>
+      <c r="F458" t="s">
+        <v>39</v>
       </c>
       <c r="G458">
         <v>82.5</v>

--- a/src/timetables/TTFINAL.xlsx
+++ b/src/timetables/TTFINAL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mr_man\Desktop\invigilation-auto\src\timetables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C80D197A-B538-4F26-B461-8DC4D9C9D1F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDCBD731-B852-4E87-8EAA-D5604D2934DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{56AEB27E-0B57-46B5-9DB8-F1AD67B47E0F}"/>
   </bookViews>
@@ -161,7 +161,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5695" uniqueCount="1458">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5695" uniqueCount="1460">
   <si>
     <t>Monday, 17 August 2026</t>
   </si>
@@ -4535,6 +4535,12 @@
   </si>
   <si>
     <t>Agyapong Dorothy Araba Yakoba</t>
+  </si>
+  <si>
+    <t>Monday, 31 August 2026</t>
+  </si>
+  <si>
+    <t>Thursday, 27 August 2026</t>
   </si>
 </sst>
 </file>
@@ -4798,7 +4804,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="130">
+  <cellXfs count="131">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -5074,6 +5080,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -42664,7 +42673,7 @@
         <v>222</v>
       </c>
       <c r="F34" t="s">
-        <v>80</v>
+        <v>39</v>
       </c>
       <c r="G34">
         <v>244.20000000000002</v>
@@ -49796,7 +49805,7 @@
     </row>
     <row r="367" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A367" t="s">
-        <v>596</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="368" spans="1:8" x14ac:dyDescent="0.35">
@@ -51134,7 +51143,7 @@
         <v>56</v>
       </c>
       <c r="F430" t="s">
-        <v>663</v>
+        <v>39</v>
       </c>
       <c r="G430">
         <v>61.600000000000009</v>
@@ -51157,7 +51166,7 @@
         <v>85</v>
       </c>
       <c r="F431" t="s">
-        <v>663</v>
+        <v>39</v>
       </c>
       <c r="G431">
         <v>93.500000000000014</v>
@@ -51180,7 +51189,7 @@
         <v>295</v>
       </c>
       <c r="F432" t="s">
-        <v>663</v>
+        <v>39</v>
       </c>
       <c r="G432">
         <v>324.5</v>
@@ -51203,7 +51212,7 @@
         <v>83</v>
       </c>
       <c r="F433" t="s">
-        <v>663</v>
+        <v>39</v>
       </c>
       <c r="G433">
         <v>91.300000000000011</v>
@@ -51226,7 +51235,7 @@
         <v>125</v>
       </c>
       <c r="F434" t="s">
-        <v>663</v>
+        <v>39</v>
       </c>
       <c r="G434">
         <v>137.5</v>
@@ -51249,7 +51258,7 @@
         <v>100</v>
       </c>
       <c r="F435" t="s">
-        <v>663</v>
+        <v>39</v>
       </c>
       <c r="G435">
         <v>110.00000000000001</v>
@@ -51272,7 +51281,7 @@
         <v>103</v>
       </c>
       <c r="F436" t="s">
-        <v>663</v>
+        <v>39</v>
       </c>
       <c r="G436">
         <v>113.30000000000001</v>
@@ -51938,7 +51947,7 @@
     </row>
     <row r="468" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A468" t="s">
-        <v>687</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="469" spans="1:8" x14ac:dyDescent="0.35">
@@ -52239,7 +52248,7 @@
     </row>
     <row r="484" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A484" t="s">
-        <v>687</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="485" spans="1:8" x14ac:dyDescent="0.35">
@@ -52540,7 +52549,7 @@
     </row>
     <row r="498" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A498" t="s">
-        <v>687</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="499" spans="1:8" x14ac:dyDescent="0.35">
@@ -52951,7 +52960,7 @@
       <c r="E515">
         <v>29</v>
       </c>
-      <c r="F515">
+      <c r="F515" s="130">
         <v>303</v>
       </c>
       <c r="G515">
